--- a/InputData/elec/SoCtMbCtbDP/Shr of Costs that Must be Covered to be Deemed Profitable.xlsx
+++ b/InputData/elec/SoCtMbCtbDP/Shr of Costs that Must be Covered to be Deemed Profitable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\RI\elec\SoCtMbCtbDP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\SoCtMbCtbDP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F978691-8E56-4E0B-8A69-98B7DC6B4375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3B09FC-ED01-4193-917B-AA2A38544B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>SoCtMbCtbDP Share of Costs that Must be Covered to be Deemed Profitable</t>
   </si>
@@ -124,9 +124,6 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
   </si>
 </sst>
 </file>
@@ -178,11 +175,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,21 +493,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DA106A-E484-4E2B-B3F9-91B326CF3E2A}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="3">
-        <v>45518</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -530,12 +520,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.5703125" customWidth="1"/>
+    <col min="1" max="1" width="34.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
@@ -543,7 +533,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -551,7 +541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -559,7 +549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -567,7 +557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -575,7 +565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -583,7 +573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -591,7 +581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -599,7 +589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -607,7 +597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -615,7 +605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -623,7 +613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -631,7 +621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -639,7 +629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -647,7 +637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -655,7 +645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -663,7 +653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -671,7 +661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -679,7 +669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -687,7 +677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -695,7 +685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -703,7 +693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -711,7 +701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -719,7 +709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -727,7 +717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>28</v>
       </c>
